--- a/data/fixtures/metadata/columns.xlsx
+++ b/data/fixtures/metadata/columns.xlsx
@@ -532,7 +532,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>product_taxes</t>
+          <t>product_taxes_less_subsidies</t>
         </is>
       </c>
     </row>

--- a/data/fixtures/metadata/columns.xlsx
+++ b/data/fixtures/metadata/columns.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,46 +503,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>eng</t>
+          <t>ava</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>wholesale_margins</t>
+          <t>trade_margins</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>det</t>
+          <t>moms</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
-        <is>
-          <t>retail_margins</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>afg</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>product_taxes_less_subsidies</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>moms</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
         <is>
           <t>vat</t>
         </is>

--- a/data/fixtures/metadata/columns.xlsx
+++ b/data/fixtures/metadata/columns.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -524,6 +524,18 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>maal</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/fixtures/metadata/columns.xlsx
+++ b/data/fixtures/metadata/columns.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -524,18 +524,6 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>maal</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>target</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
